--- a/server/xlsx/装备模板表.xlsx
+++ b/server/xlsx/装备模板表.xlsx
@@ -4,10 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="17760" windowHeight="8085" firstSheet="3"/>
+    <workbookView windowWidth="27045" windowHeight="12060" firstSheet="3"/>
   </bookViews>
   <sheets>
-    <sheet name="装备模板表" sheetId="5" r:id="rId1"/>
+    <sheet name="装备模板表_修仙" sheetId="5" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="17">
   <si>
     <t>id</t>
   </si>
@@ -38,9 +38,6 @@
     <t>怪物名称</t>
   </si>
   <si>
-    <t>体系</t>
-  </si>
-  <si>
     <t>属性基数</t>
   </si>
   <si>
@@ -50,9 +47,6 @@
     <t>name</t>
   </si>
   <si>
-    <t>sys</t>
-  </si>
-  <si>
     <t>生命值</t>
   </si>
   <si>
@@ -84,9 +78,6 @@
   </si>
   <si>
     <t>测试装备</t>
-  </si>
-  <si>
-    <t>修仙</t>
   </si>
 </sst>
 </file>
@@ -465,7 +456,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -606,17 +597,6 @@
         <color rgb="FFEBEBEB"/>
       </left>
       <right/>
-      <top style="thin">
-        <color rgb="FFEBEBEB"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFEBEBEB"/>
-      </right>
       <top style="thin">
         <color rgb="FFEBEBEB"/>
       </top>
@@ -747,7 +727,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -759,34 +739,34 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -871,7 +851,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -906,9 +886,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
@@ -1024,7 +1001,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="黑色浅色系标题行表格样式" count="2" xr9:uid="{CA6061CE-2096-43AA-B12D-C8836CA6E1D9}">
+    <tableStyle name="黑色浅色系标题行表格样式" count="2" xr9:uid="{DE9C6AFD-840B-48A3-BA57-5B18D63043B6}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -1324,19 +1301,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="9.84166666666667" customWidth="1"/>
     <col min="2" max="2" width="10.3416666666667" customWidth="1"/>
     <col min="3" max="3" width="12.3416666666667" customWidth="1"/>
-    <col min="4" max="5" width="10.3416666666667" customWidth="1"/>
-    <col min="6" max="6" width="7.125" customWidth="1"/>
-    <col min="11" max="11" width="11.25" customWidth="1"/>
-    <col min="12" max="12" width="11" customWidth="1"/>
+    <col min="4" max="4" width="10.3416666666667" customWidth="1"/>
+    <col min="5" max="5" width="7.125" customWidth="1"/>
+    <col min="10" max="10" width="11.25" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1" spans="1:12">
+    <row r="1" ht="22.5" customHeight="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1346,97 +1323,88 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
+      <c r="E1" s="4"/>
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
       <c r="I1" s="4"/>
       <c r="J1" s="4"/>
       <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
     </row>
-    <row r="2" ht="22.5" customHeight="1" spans="1:12">
+    <row r="2" ht="22.5" customHeight="1" spans="1:11">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F2" t="s">
         <v>8</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>9</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>10</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>11</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>12</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>13</v>
       </c>
-      <c r="K2" t="s">
+    </row>
+    <row r="3" ht="22.5" customHeight="1" spans="1:11">
+      <c r="A3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="L2" t="s">
+      <c r="B3" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>15</v>
       </c>
+      <c r="E3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="3" ht="22.5" customHeight="1" spans="1:12">
-      <c r="A3" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" ht="39" customHeight="1" spans="1:12">
+    <row r="4" ht="39" customHeight="1" spans="1:11">
       <c r="A4" s="9">
         <v>1</v>
       </c>
@@ -1444,48 +1412,45 @@
         <v>17</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="10">
+        <v>16</v>
+      </c>
+      <c r="D4" s="10">
         <v>100</v>
       </c>
+      <c r="E4">
+        <v>100</v>
+      </c>
       <c r="F4">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
         <v>1</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>0</v>
       </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
       <c r="J4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K4">
         <v>10</v>
       </c>
-      <c r="L4">
-        <v>10</v>
-      </c>
     </row>
-    <row r="5" spans="5:5">
-      <c r="E5" s="13"/>
+    <row r="5" spans="4:4">
+      <c r="D5" s="12"/>
     </row>
-    <row r="6" spans="5:5">
-      <c r="E6" s="13"/>
+    <row r="6" spans="4:4">
+      <c r="D6" s="12"/>
     </row>
-    <row r="7" spans="5:5">
-      <c r="E7" s="13"/>
+    <row r="7" spans="4:4">
+      <c r="D7" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="E1:L1"/>
+    <mergeCell ref="D1:K1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
